--- a/reports/jobs_2026-10-22.xlsx
+++ b/reports/jobs_2026-10-22.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Zscaler India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Escalation Engineer</t>
+          <t>CEO AI billing software built for founders who ship fast</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -538,11 +538,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, IND</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -550,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
+          <t>https://www.chargebee.com/solutions/role/ceo/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1103,17 +1099,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Theorem Proving Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1129,12 +1125,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1146,17 +1142,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Compiler Engineer (Machine Learning)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1164,11 +1160,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1176,12 +1168,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1198,12 +1190,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1211,11 +1203,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1223,7 +1211,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1245,12 +1233,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1270,7 +1258,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1292,12 +1280,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Systems Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1317,7 +1305,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27796</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1339,12 +1327,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1352,7 +1340,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1360,7 +1352,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/25283</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1382,12 +1374,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1407,7 +1399,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1429,12 +1421,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Principle Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1444,7 +1436,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1454,7 +1446,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25283</t>
+          <t>https://www.atlassian.com/company/careers/details/27796</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1489,11 +1481,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1501,7 +1489,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27794</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1523,12 +1511,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1548,7 +1536,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25566</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1570,12 +1558,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1583,7 +1571,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1591,7 +1583,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://www.atlassian.com/company/careers/details/27794</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1613,7 +1605,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1638,7 +1630,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/25566</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1660,7 +1652,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning System Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1673,11 +1665,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1685,7 +1673,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27388</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1707,12 +1695,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1732,7 +1720,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1754,12 +1742,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Machine Learning System Engineer</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1767,7 +1755,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1775,7 +1767,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/27388</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1797,7 +1789,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1810,7 +1802,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1818,7 +1814,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1840,12 +1836,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1861,7 +1857,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1883,7 +1879,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1904,7 +1900,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1926,12 +1922,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1939,11 +1935,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1951,7 +1943,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1973,12 +1965,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1986,11 +1978,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -1998,7 +1986,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2020,7 +2008,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2045,7 +2033,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2067,12 +2055,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2080,7 +2068,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2088,7 +2080,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2110,7 +2102,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2123,7 +2115,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2131,7 +2127,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2153,12 +2149,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2174,7 +2170,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2196,7 +2192,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2217,7 +2213,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2239,7 +2235,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2252,11 +2248,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2264,7 +2256,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2286,7 +2278,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2307,7 +2299,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2329,12 +2321,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2354,7 +2346,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2376,12 +2368,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2389,11 +2381,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2401,7 +2389,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26986</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2423,12 +2411,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2438,7 +2426,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2448,7 +2436,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2465,12 +2453,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2483,7 +2471,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2491,12 +2483,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/details/26986</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2508,17 +2500,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2526,7 +2518,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2534,12 +2530,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2551,12 +2547,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2569,11 +2565,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2581,12 +2573,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2598,17 +2590,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2616,11 +2608,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2628,12 +2616,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2650,7 +2638,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2675,7 +2663,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2697,12 +2685,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2722,7 +2710,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2744,12 +2732,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2757,7 +2745,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2765,7 +2757,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2787,7 +2779,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2802,7 +2794,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2812,7 +2804,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2834,12 +2826,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2847,11 +2839,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -2859,7 +2847,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2881,7 +2869,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2906,7 +2894,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2928,7 +2916,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2953,7 +2941,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2975,7 +2963,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3000,7 +2988,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3022,12 +3010,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3047,7 +3035,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3069,7 +3057,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3094,7 +3082,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3116,7 +3104,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Developer - 3 (Voice4Ai-Backend)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3141,7 +3129,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-voice4aibackend</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3158,17 +3146,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3176,7 +3164,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3184,12 +3176,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3201,17 +3193,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3219,7 +3211,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3227,12 +3223,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3249,12 +3245,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>GenAI-Engineer</t>
+          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3270,7 +3266,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3292,12 +3288,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3313,7 +3309,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Engineer_SR-46455-1</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer---AWS_SR-37522</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3330,12 +3326,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>GenAI-Engineer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3356,12 +3352,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/GenAI-Engineer_SR-46807</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3373,17 +3369,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3399,12 +3395,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3421,12 +3417,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3442,7 +3438,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3459,17 +3455,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3477,11 +3473,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3489,12 +3481,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3506,17 +3498,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3526,7 +3518,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3536,12 +3528,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3553,12 +3545,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3573,7 +3565,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3583,12 +3575,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3600,17 +3592,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3620,7 +3612,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3630,12 +3622,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3647,17 +3639,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3665,7 +3657,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3673,12 +3669,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3695,12 +3691,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3716,7 +3712,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -3733,12 +3729,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3751,11 +3747,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3763,12 +3755,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3785,7 +3777,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3800,7 +3792,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3810,7 +3802,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -3827,12 +3819,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3845,7 +3837,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3853,12 +3849,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3870,12 +3866,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3888,11 +3884,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3900,12 +3892,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3917,17 +3909,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3935,7 +3927,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3943,12 +3939,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3960,17 +3956,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Careers Hiring across engineering, design, product, GTM &amp; ops.</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3978,11 +3974,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>India’s 100 th unicorn. C</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -3990,12 +3982,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4007,17 +3999,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4033,12 +4025,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4050,12 +4042,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4068,11 +4060,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4080,12 +4068,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4102,7 +4090,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4117,7 +4105,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4127,7 +4115,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4149,7 +4137,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4164,7 +4152,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4174,7 +4162,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4196,7 +4184,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4221,7 +4209,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4243,7 +4231,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4258,7 +4246,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -4268,7 +4256,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4290,7 +4278,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4305,7 +4293,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4315,7 +4303,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -4337,7 +4325,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition- Intern || Noida ||</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4362,7 +4350,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/648841ab-2778-4759-a4c9-eabae97ec65d</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4379,17 +4367,17 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition- Intern || Noida ||</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4397,7 +4385,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4405,12 +4397,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/648841ab-2778-4759-a4c9-eabae97ec65d</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4422,17 +4414,17 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4440,11 +4432,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4452,12 +4440,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -4474,12 +4462,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4499,7 +4487,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4521,12 +4509,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4546,7 +4534,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -4563,17 +4551,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4581,7 +4569,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4589,12 +4581,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4606,12 +4598,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4624,11 +4616,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4636,12 +4624,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4658,12 +4646,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4683,7 +4671,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -4705,7 +4693,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4720,7 +4708,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -4730,7 +4718,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -4752,7 +4740,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4762,12 +4750,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4777,7 +4765,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -4799,7 +4787,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4809,12 +4797,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>0-2 years</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t xml:space="preserve">Bangalore </t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -4824,7 +4812,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -4841,17 +4829,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4861,7 +4849,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -4871,12 +4859,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4888,17 +4876,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4906,7 +4894,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -4914,12 +4906,12 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -4936,12 +4928,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4957,7 +4949,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzgsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -4979,7 +4971,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5000,7 +4992,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5022,7 +5014,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5043,7 +5035,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5065,7 +5057,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5086,7 +5078,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -5103,17 +5095,17 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5121,11 +5113,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -5133,12 +5121,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5155,12 +5143,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5180,7 +5168,7 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -5197,17 +5185,17 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -5215,7 +5203,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -5223,12 +5215,12 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -5240,12 +5232,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5266,12 +5258,12 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5283,12 +5275,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -5301,11 +5293,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
@@ -5313,12 +5301,12 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5330,12 +5318,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5350,7 +5338,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon, India; Pune, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -5360,12 +5348,12 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5468,8 +5456,55 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Zscaler India</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Escalation Engineer</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zscaler</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I110"/>
+  <autoFilter ref="A1:I111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5580,6 +5615,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5591,7 +5627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5639,15 +5675,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.indmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5656,18 +5712,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5676,18 +5732,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5696,18 +5752,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5716,18 +5772,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5736,18 +5792,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5756,18 +5812,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5776,18 +5832,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -5796,18 +5852,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5816,18 +5872,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5836,18 +5892,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -5856,18 +5932,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Swiggy</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://careers.swiggy.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5876,18 +5952,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -5896,18 +5972,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -5916,18 +5992,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
